--- a/144/DQ Templates and Instructions/Topic 4 DQ 1/Topic 4 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 4 DQ 1/Topic 4 DQ 1.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 4 DQ 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="412" documentId="8_{3C829CDA-585B-40ED-A74D-EC300311E87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01E5E134-2164-4823-8E2C-54CF50B12056}"/>
+  <xr:revisionPtr revIDLastSave="418" documentId="8_{3C829CDA-585B-40ED-A74D-EC300311E87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96924DAE-DA90-4F88-89DB-4E29EF08667E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{205DC2E6-2D69-4C44-AD14-EEFE253664E7}"/>
+    <workbookView xWindow="30" yWindow="390" windowWidth="28770" windowHeight="15270" xr2:uid="{205DC2E6-2D69-4C44-AD14-EEFE253664E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="3" r:id="rId1"/>
-    <sheet name="Budget" sheetId="1" r:id="rId2"/>
-    <sheet name="Percentage Change" sheetId="6" r:id="rId3"/>
-    <sheet name="Soln" sheetId="5" state="hidden" r:id="rId4"/>
-    <sheet name="Soln2" sheetId="7" state="hidden" r:id="rId5"/>
-    <sheet name="Income" sheetId="2" state="hidden" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="4" state="hidden" r:id="rId7"/>
+    <sheet name="Users" sheetId="8" state="hidden" r:id="rId2"/>
+    <sheet name="Budget" sheetId="1" r:id="rId3"/>
+    <sheet name="Percentage Change" sheetId="6" r:id="rId4"/>
+    <sheet name="Soln" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Soln2" sheetId="7" state="hidden" r:id="rId6"/>
+    <sheet name="Income" sheetId="2" state="hidden" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="4" state="hidden" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="78">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -466,6 +467,12 @@
   <si>
     <t>Video for this cell</t>
   </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
 </sst>
 </file>
 
@@ -474,7 +481,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,12 +575,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="16"/>
       <color theme="10"/>
@@ -587,12 +588,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1167,7 +1162,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
@@ -1229,13 +1224,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1269,25 +1263,25 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1310,26 +1304,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1353,6 +1341,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1418,6 +1412,161 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1426,156 +1575,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1585,19 +1584,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2220,61 +2215,61 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="57" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="63" t="s">
+      <c r="B2" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="65"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="64"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="68"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="67"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="68"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="67"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="66"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="68"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="67"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="D6" s="69"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="71"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="70"/>
     </row>
     <row r="8" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="54" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="18"/>
@@ -2283,17 +2278,17 @@
       <c r="G8" s="18"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="48" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="48" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2307,6 +2302,172 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F6C606-3164-4B0A-B643-9E217F8F371C}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="133"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="133" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="134">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>Budget!C2</f>
+        <v>Your Name Here</v>
+      </c>
+      <c r="F1" s="135" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="133" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="133" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="133" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>bob</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="133" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v>bob</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="133" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name Here</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Vy23Gj6nI0zMZRM0Au2g5W3aGhP7gxkn2QqIF138Jube+0rICtrk3XDRsWn/TVlaZMaiiozIjbSZF8GG+ONesw==" saltValue="633A4zc//YJzYTFkFhDDlg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DCC803D-65A0-4D9D-9D2F-35F6192494FC}">
   <dimension ref="B1:S40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2321,57 +2482,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D1" s="33"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="2:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="133" t="s">
+      <c r="D2" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="27"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="134" t="s">
+      <c r="D3" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="101" t="s">
+      <c r="E3" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="103"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="102"/>
     </row>
     <row r="4" spans="2:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="135"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="106"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="105"/>
     </row>
     <row r="5" spans="2:11" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="136"/>
+      <c r="D5" s="61"/>
     </row>
     <row r="6" spans="2:11" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="81" t="s">
+      <c r="B6" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="82"/>
-      <c r="E6" s="107" t="s">
+      <c r="C6" s="81"/>
+      <c r="E6" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="109"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="108"/>
     </row>
     <row r="7" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
@@ -2380,17 +2541,17 @@
       <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="31">
         <v>15</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="F7" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="88"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="87"/>
     </row>
     <row r="8" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
@@ -2399,17 +2560,17 @@
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="28">
         <v>15</v>
       </c>
-      <c r="F8" s="89" t="s">
+      <c r="F8" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="91"/>
+      <c r="G8" s="89"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="89"/>
+      <c r="J8" s="89"/>
+      <c r="K8" s="90"/>
     </row>
     <row r="9" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
@@ -2418,17 +2579,17 @@
       <c r="C9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>16</v>
       </c>
-      <c r="F9" s="86" t="s">
+      <c r="F9" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="88"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="87"/>
     </row>
     <row r="10" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
@@ -2437,17 +2598,17 @@
       <c r="C10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>16</v>
       </c>
-      <c r="F10" s="98" t="s">
+      <c r="F10" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="99"/>
-      <c r="K10" s="100"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="99"/>
     </row>
     <row r="11" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
@@ -2458,56 +2619,56 @@
       </c>
     </row>
     <row r="12" spans="2:11" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="82" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="65"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="64"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="94"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="110"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="68"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="93"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="67"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="95"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="97"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="71"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="95"/>
+      <c r="D14" s="96"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="70"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="35" t="s">
+      <c r="G15" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="35" t="s">
+      <c r="H15" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="35" t="s">
+      <c r="I15" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="K15" s="35" t="s">
+      <c r="K15" s="34" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2518,356 +2679,356 @@
       <c r="D16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="36"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="38"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="37"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="38"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="37"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="38"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="37"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="38"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="37"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
     </row>
     <row r="22" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="38"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="37"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
     </row>
     <row r="23" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D24" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
     </row>
     <row r="25" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="65"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
+      <c r="C25" s="64"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
     </row>
     <row r="26" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="66"/>
-      <c r="C26" s="68"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="36"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="67"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
     </row>
     <row r="27" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="66"/>
-      <c r="C27" s="68"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="67"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
     </row>
     <row r="28" spans="2:19" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="69"/>
-      <c r="C28" s="71"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="70"/>
     </row>
     <row r="29" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E29" s="72" t="s">
+      <c r="E29" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="74"/>
-      <c r="M29" s="72" t="s">
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="M29" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="N29" s="73"/>
-      <c r="O29" s="73"/>
-      <c r="P29" s="73"/>
-      <c r="Q29" s="73"/>
-      <c r="R29" s="73"/>
-      <c r="S29" s="74"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="73"/>
     </row>
     <row r="30" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="83" t="s">
+      <c r="B30" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="65"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="77"/>
-      <c r="M30" s="75"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="76"/>
-      <c r="Q30" s="76"/>
-      <c r="R30" s="76"/>
-      <c r="S30" s="77"/>
+      <c r="C30" s="64"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="76"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="75"/>
+      <c r="P30" s="75"/>
+      <c r="Q30" s="75"/>
+      <c r="R30" s="75"/>
+      <c r="S30" s="76"/>
     </row>
     <row r="31" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="66"/>
-      <c r="C31" s="68"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="77"/>
-      <c r="M31" s="75"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="76"/>
-      <c r="P31" s="76"/>
-      <c r="Q31" s="76"/>
-      <c r="R31" s="76"/>
-      <c r="S31" s="77"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="67"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="76"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="75"/>
+      <c r="P31" s="75"/>
+      <c r="Q31" s="75"/>
+      <c r="R31" s="75"/>
+      <c r="S31" s="76"/>
     </row>
     <row r="32" spans="2:19" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="66"/>
-      <c r="C32" s="68"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="77"/>
-      <c r="M32" s="75"/>
-      <c r="N32" s="76"/>
-      <c r="O32" s="76"/>
-      <c r="P32" s="76"/>
-      <c r="Q32" s="76"/>
-      <c r="R32" s="76"/>
-      <c r="S32" s="77"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="67"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="76"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="75"/>
+      <c r="P32" s="75"/>
+      <c r="Q32" s="75"/>
+      <c r="R32" s="75"/>
+      <c r="S32" s="76"/>
     </row>
     <row r="33" spans="2:19" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="69"/>
-      <c r="C33" s="71"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="77"/>
-      <c r="M33" s="75"/>
-      <c r="N33" s="76"/>
-      <c r="O33" s="76"/>
-      <c r="P33" s="76"/>
-      <c r="Q33" s="76"/>
-      <c r="R33" s="76"/>
-      <c r="S33" s="77"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="70"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="76"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="75"/>
+      <c r="P33" s="75"/>
+      <c r="Q33" s="75"/>
+      <c r="R33" s="75"/>
+      <c r="S33" s="76"/>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E34" s="75"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
-      <c r="K34" s="77"/>
-      <c r="M34" s="75"/>
-      <c r="N34" s="76"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="76"/>
-      <c r="Q34" s="76"/>
-      <c r="R34" s="76"/>
-      <c r="S34" s="77"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="75"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="76"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="75"/>
+      <c r="P34" s="75"/>
+      <c r="Q34" s="75"/>
+      <c r="R34" s="75"/>
+      <c r="S34" s="76"/>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E35" s="75"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="77"/>
-      <c r="M35" s="75"/>
-      <c r="N35" s="76"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="76"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="77"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="75"/>
+      <c r="J35" s="75"/>
+      <c r="K35" s="76"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="75"/>
+      <c r="P35" s="75"/>
+      <c r="Q35" s="75"/>
+      <c r="R35" s="75"/>
+      <c r="S35" s="76"/>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E36" s="75"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="76"/>
-      <c r="K36" s="77"/>
-      <c r="M36" s="75"/>
-      <c r="N36" s="76"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="76"/>
-      <c r="Q36" s="76"/>
-      <c r="R36" s="76"/>
-      <c r="S36" s="77"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
+      <c r="J36" s="75"/>
+      <c r="K36" s="76"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="75"/>
+      <c r="P36" s="75"/>
+      <c r="Q36" s="75"/>
+      <c r="R36" s="75"/>
+      <c r="S36" s="76"/>
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E37" s="75"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="76"/>
-      <c r="K37" s="77"/>
-      <c r="M37" s="75"/>
-      <c r="N37" s="76"/>
-      <c r="O37" s="76"/>
-      <c r="P37" s="76"/>
-      <c r="Q37" s="76"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="77"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="76"/>
+      <c r="M37" s="74"/>
+      <c r="N37" s="75"/>
+      <c r="O37" s="75"/>
+      <c r="P37" s="75"/>
+      <c r="Q37" s="75"/>
+      <c r="R37" s="75"/>
+      <c r="S37" s="76"/>
     </row>
     <row r="38" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E38" s="75"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="77"/>
-      <c r="M38" s="75"/>
-      <c r="N38" s="76"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="76"/>
-      <c r="Q38" s="76"/>
-      <c r="R38" s="76"/>
-      <c r="S38" s="77"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="76"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="75"/>
+      <c r="P38" s="75"/>
+      <c r="Q38" s="75"/>
+      <c r="R38" s="75"/>
+      <c r="S38" s="76"/>
     </row>
     <row r="39" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="75"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="77"/>
-      <c r="M39" s="75"/>
-      <c r="N39" s="76"/>
-      <c r="O39" s="76"/>
-      <c r="P39" s="76"/>
-      <c r="Q39" s="76"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="77"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+      <c r="J39" s="75"/>
+      <c r="K39" s="76"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="75"/>
+      <c r="P39" s="75"/>
+      <c r="Q39" s="75"/>
+      <c r="R39" s="75"/>
+      <c r="S39" s="76"/>
     </row>
     <row r="40" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E40" s="78"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="80"/>
-      <c r="M40" s="78"/>
-      <c r="N40" s="79"/>
-      <c r="O40" s="79"/>
-      <c r="P40" s="79"/>
-      <c r="Q40" s="79"/>
-      <c r="R40" s="79"/>
-      <c r="S40" s="80"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
+      <c r="J40" s="78"/>
+      <c r="K40" s="79"/>
+      <c r="M40" s="77"/>
+      <c r="N40" s="78"/>
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="78"/>
+      <c r="R40" s="78"/>
+      <c r="S40" s="79"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="9l8gJOf7bmHg0E+pecKvgY9rbixgCaeEA9wQgFhyXrwKF3HW12rHp+16vcbnJSohe3eJoygMIRAvdBk1E9C+Qg==" saltValue="kCzTCaIjsc/v+OenjNhBNA==" spinCount="100000" sheet="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
@@ -2922,7 +3083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{049149D3-C31D-4474-A186-04CB99D57D70}">
   <dimension ref="B2:S22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2936,34 +3097,34 @@
     <row r="2" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="64" t="s">
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="M4" s="81" t="s">
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="64"/>
+      <c r="M4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="82"/>
+      <c r="N4" s="81"/>
     </row>
     <row r="5" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="66"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="67"/>
       <c r="M5" s="3" t="s">
         <v>9</v>
       </c>
@@ -2972,15 +3133,15 @@
       </c>
     </row>
     <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="66"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="70"/>
       <c r="M6" s="5" t="s">
         <v>11</v>
       </c>
@@ -2989,17 +3150,17 @@
       </c>
     </row>
     <row r="7" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="69"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="111" t="s">
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="113"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
       <c r="M7" s="7" t="s">
         <v>13</v>
       </c>
@@ -3008,19 +3169,19 @@
       </c>
     </row>
     <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="117" t="s">
+      <c r="B8" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="114" t="s">
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="125" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="115"/>
-      <c r="I8" s="116"/>
-      <c r="J8" s="53"/>
+      <c r="H8" s="126"/>
+      <c r="I8" s="127"/>
+      <c r="J8" s="51"/>
       <c r="M8" s="8" t="s">
         <v>15</v>
       </c>
@@ -3029,17 +3190,17 @@
       </c>
     </row>
     <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="120"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="59"/>
-      <c r="G9" s="111" t="s">
+      <c r="B9" s="112"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
       <c r="M9" s="9" t="s">
         <v>17</v>
       </c>
@@ -3048,236 +3209,226 @@
       </c>
     </row>
     <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="123"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="53"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="51"/>
     </row>
     <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="117" t="s">
+      <c r="B11" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="53"/>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="51"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
-      <c r="M11" s="107" t="s">
+      <c r="M11" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="108"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="108"/>
-      <c r="S11" s="109"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="107"/>
+      <c r="P11" s="107"/>
+      <c r="Q11" s="107"/>
+      <c r="R11" s="107"/>
+      <c r="S11" s="108"/>
     </row>
     <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="120"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="126" t="s">
+      <c r="B12" s="112"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="128"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="124"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
-      <c r="M12" s="32">
+      <c r="M12" s="31">
         <v>15</v>
       </c>
-      <c r="N12" s="86" t="s">
+      <c r="N12" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="O12" s="87"/>
-      <c r="P12" s="87"/>
-      <c r="Q12" s="87"/>
-      <c r="R12" s="87"/>
-      <c r="S12" s="88"/>
+      <c r="O12" s="86"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="86"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="87"/>
     </row>
     <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="123"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="53"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="51"/>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
-      <c r="M13" s="29">
+      <c r="M13" s="28">
         <v>15</v>
       </c>
-      <c r="N13" s="89" t="s">
+      <c r="N13" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="91"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="89"/>
+      <c r="Q13" s="89"/>
+      <c r="R13" s="89"/>
+      <c r="S13" s="90"/>
     </row>
     <row r="14" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="53"/>
-      <c r="M14" s="30">
+      <c r="C14" s="110"/>
+      <c r="D14" s="110"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="51"/>
+      <c r="M14" s="29">
         <v>16</v>
       </c>
-      <c r="N14" s="86" t="s">
+      <c r="N14" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="O14" s="87"/>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="88"/>
+      <c r="O14" s="86"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="86"/>
+      <c r="R14" s="86"/>
+      <c r="S14" s="87"/>
     </row>
     <row r="15" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="120"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="111" t="s">
+      <c r="B15" s="112"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="112"/>
-      <c r="I15" s="112"/>
-      <c r="J15" s="113"/>
-      <c r="M15" s="31">
+      <c r="H15" s="120"/>
+      <c r="I15" s="120"/>
+      <c r="J15" s="121"/>
+      <c r="M15" s="30">
         <v>16</v>
       </c>
-      <c r="N15" s="98" t="s">
+      <c r="N15" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="99"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="99"/>
-      <c r="S15" s="100"/>
+      <c r="O15" s="98"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="98"/>
+      <c r="R15" s="98"/>
+      <c r="S15" s="99"/>
     </row>
     <row r="16" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="123"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="53"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="51"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117" t="s">
+      <c r="B17" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="53"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="51"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="120"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="111" t="s">
+      <c r="B18" s="112"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="56"/>
+      <c r="G18" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="112"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="113"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="123"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="124"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="53"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="51"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="117" t="s">
+      <c r="B20" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="53"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="51"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="120"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="61"/>
-      <c r="G21" s="111" t="s">
+      <c r="B21" s="112"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="112"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="113"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="120"/>
+      <c r="J21" s="121"/>
     </row>
     <row r="22" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="123"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="124"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="44"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="43"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="NfkF4yj+iEgixxkXgGkXwfbmeur8zEMZzhBeiga1PAe+znO1CUs+dZQfNrUkZLGRoA+B1vX0leFgze0sCGq/qA==" saltValue="MqF1cxQrqY3f4SjF1BynVg==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="20">
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="B11:E13"/>
-    <mergeCell ref="B4:E7"/>
-    <mergeCell ref="B14:E16"/>
-    <mergeCell ref="B17:E19"/>
-    <mergeCell ref="B20:E22"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="N15:S15"/>
-    <mergeCell ref="G12:J12"/>
     <mergeCell ref="F4:J6"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="G9:J9"/>
@@ -3288,6 +3439,16 @@
     <mergeCell ref="N13:S13"/>
     <mergeCell ref="N14:S14"/>
     <mergeCell ref="G8:I8"/>
+    <mergeCell ref="B20:E22"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="N15:S15"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="B11:E13"/>
+    <mergeCell ref="B4:E7"/>
+    <mergeCell ref="B14:E16"/>
+    <mergeCell ref="B17:E19"/>
   </mergeCells>
   <conditionalFormatting sqref="F7 F9 F12 F15 F18 F21">
     <cfRule type="expression" dxfId="1" priority="1">
@@ -3321,7 +3482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFEB4FCF-57FF-4563-83C9-84D8EB6784D0}">
   <dimension ref="B1:S40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3336,46 +3497,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D1" s="33"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="2:11" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="27"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="128" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="101" t="s">
+      <c r="E3" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="103"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="102"/>
     </row>
     <row r="4" spans="2:11" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="85"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="106"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="105"/>
     </row>
     <row r="5" spans="2:11" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="81" t="s">
+      <c r="B5" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="33"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="32"/>
     </row>
     <row r="6" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
@@ -3384,15 +3545,15 @@
       <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="107" t="s">
+      <c r="E6" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="109"/>
+      <c r="F6" s="107"/>
+      <c r="G6" s="107"/>
+      <c r="H6" s="107"/>
+      <c r="I6" s="107"/>
+      <c r="J6" s="107"/>
+      <c r="K6" s="108"/>
     </row>
     <row r="7" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
@@ -3401,17 +3562,17 @@
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="31">
         <v>15</v>
       </c>
-      <c r="F7" s="86" t="s">
+      <c r="F7" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="88"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="87"/>
     </row>
     <row r="8" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
@@ -3420,17 +3581,17 @@
       <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="28">
         <v>15</v>
       </c>
-      <c r="F8" s="89" t="s">
+      <c r="F8" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="90"/>
-      <c r="H8" s="90"/>
-      <c r="I8" s="90"/>
-      <c r="J8" s="90"/>
-      <c r="K8" s="91"/>
+      <c r="G8" s="89"/>
+      <c r="H8" s="89"/>
+      <c r="I8" s="89"/>
+      <c r="J8" s="89"/>
+      <c r="K8" s="90"/>
     </row>
     <row r="9" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
@@ -3439,17 +3600,17 @@
       <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>16</v>
       </c>
-      <c r="F9" s="86" t="s">
+      <c r="F9" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="87"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="88"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="86"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="87"/>
     </row>
     <row r="10" spans="2:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
@@ -3458,44 +3619,44 @@
       <c r="C10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>16</v>
       </c>
-      <c r="F10" s="98" t="s">
+      <c r="F10" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="99"/>
-      <c r="H10" s="99"/>
-      <c r="I10" s="99"/>
-      <c r="J10" s="99"/>
-      <c r="K10" s="100"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="99"/>
     </row>
     <row r="11" spans="2:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="83" t="s">
+      <c r="F12" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="64"/>
-      <c r="K12" s="65"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="64"/>
     </row>
     <row r="13" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="94"/>
-      <c r="F13" s="69"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="71"/>
+      <c r="C13" s="93"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="70"/>
     </row>
     <row r="14" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="95"/>
-      <c r="C14" s="97"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="96"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F15" s="11" t="s">
@@ -3590,7 +3751,7 @@
       <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="12">
         <f>SUM(G16:G27)</f>
         <v>0</v>
       </c>
@@ -3627,7 +3788,7 @@
       <c r="B19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="12">
         <f>SUM(H16:H27)</f>
         <v>0</v>
       </c>
@@ -3664,7 +3825,7 @@
       <c r="B20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="12">
         <f>SUM(I16:I27)</f>
         <v>0</v>
       </c>
@@ -3701,7 +3862,7 @@
       <c r="B21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="12">
         <f>SUM(J16:J27)</f>
         <v>0</v>
       </c>
@@ -3738,7 +3899,7 @@
       <c r="B22" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="22">
         <f>SUM(K16:K27)</f>
         <v>0</v>
       </c>
@@ -3775,11 +3936,11 @@
       <c r="B23" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="23">
         <f>SUM(C17:C22)</f>
         <v>0</v>
       </c>
-      <c r="D23" s="25" t="e">
+      <c r="D23" s="24" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
@@ -3838,10 +3999,10 @@
       </c>
     </row>
     <row r="25" spans="2:19" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="82" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="65"/>
+      <c r="C25" s="64"/>
       <c r="F25" s="19">
         <f>Budget!F25</f>
         <v>0</v>
@@ -3868,8 +4029,8 @@
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B26" s="66"/>
-      <c r="C26" s="68"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="67"/>
       <c r="F26" s="19">
         <f>Budget!F26</f>
         <v>0</v>
@@ -3896,8 +4057,8 @@
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B27" s="66"/>
-      <c r="C27" s="68"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="67"/>
       <c r="F27" s="19">
         <f>Budget!F27</f>
         <v>0</v>
@@ -3924,222 +4085,216 @@
       </c>
     </row>
     <row r="28" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="69"/>
-      <c r="C28" s="71"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="70"/>
     </row>
     <row r="29" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E29" s="72" t="s">
+      <c r="E29" s="71" t="s">
         <v>37</v>
       </c>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
-      <c r="J29" s="73"/>
-      <c r="K29" s="74"/>
-      <c r="M29" s="72" t="s">
+      <c r="F29" s="72"/>
+      <c r="G29" s="72"/>
+      <c r="H29" s="72"/>
+      <c r="I29" s="72"/>
+      <c r="J29" s="72"/>
+      <c r="K29" s="73"/>
+      <c r="M29" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="N29" s="73"/>
-      <c r="O29" s="73"/>
-      <c r="P29" s="73"/>
-      <c r="Q29" s="73"/>
-      <c r="R29" s="73"/>
-      <c r="S29" s="74"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="73"/>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B30" s="83" t="s">
+      <c r="B30" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="65"/>
-      <c r="E30" s="75"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="76"/>
-      <c r="H30" s="76"/>
-      <c r="I30" s="76"/>
-      <c r="J30" s="76"/>
-      <c r="K30" s="77"/>
-      <c r="M30" s="75"/>
-      <c r="N30" s="76"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="76"/>
-      <c r="Q30" s="76"/>
-      <c r="R30" s="76"/>
-      <c r="S30" s="77"/>
+      <c r="C30" s="64"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="75"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="76"/>
+      <c r="M30" s="74"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="75"/>
+      <c r="P30" s="75"/>
+      <c r="Q30" s="75"/>
+      <c r="R30" s="75"/>
+      <c r="S30" s="76"/>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B31" s="66"/>
-      <c r="C31" s="68"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="77"/>
-      <c r="M31" s="75"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="76"/>
-      <c r="P31" s="76"/>
-      <c r="Q31" s="76"/>
-      <c r="R31" s="76"/>
-      <c r="S31" s="77"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="67"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="76"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="75"/>
+      <c r="O31" s="75"/>
+      <c r="P31" s="75"/>
+      <c r="Q31" s="75"/>
+      <c r="R31" s="75"/>
+      <c r="S31" s="76"/>
     </row>
     <row r="32" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="69"/>
-      <c r="C32" s="71"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="77"/>
-      <c r="M32" s="75"/>
-      <c r="N32" s="76"/>
-      <c r="O32" s="76"/>
-      <c r="P32" s="76"/>
-      <c r="Q32" s="76"/>
-      <c r="R32" s="76"/>
-      <c r="S32" s="77"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="70"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="76"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="75"/>
+      <c r="P32" s="75"/>
+      <c r="Q32" s="75"/>
+      <c r="R32" s="75"/>
+      <c r="S32" s="76"/>
     </row>
     <row r="33" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E33" s="75"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
-      <c r="J33" s="76"/>
-      <c r="K33" s="77"/>
-      <c r="M33" s="75"/>
-      <c r="N33" s="76"/>
-      <c r="O33" s="76"/>
-      <c r="P33" s="76"/>
-      <c r="Q33" s="76"/>
-      <c r="R33" s="76"/>
-      <c r="S33" s="77"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="76"/>
+      <c r="M33" s="74"/>
+      <c r="N33" s="75"/>
+      <c r="O33" s="75"/>
+      <c r="P33" s="75"/>
+      <c r="Q33" s="75"/>
+      <c r="R33" s="75"/>
+      <c r="S33" s="76"/>
     </row>
     <row r="34" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E34" s="75"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
-      <c r="K34" s="77"/>
-      <c r="M34" s="75"/>
-      <c r="N34" s="76"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="76"/>
-      <c r="Q34" s="76"/>
-      <c r="R34" s="76"/>
-      <c r="S34" s="77"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="75"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="76"/>
+      <c r="M34" s="74"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="75"/>
+      <c r="P34" s="75"/>
+      <c r="Q34" s="75"/>
+      <c r="R34" s="75"/>
+      <c r="S34" s="76"/>
     </row>
     <row r="35" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E35" s="75"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="77"/>
-      <c r="M35" s="75"/>
-      <c r="N35" s="76"/>
-      <c r="O35" s="76"/>
-      <c r="P35" s="76"/>
-      <c r="Q35" s="76"/>
-      <c r="R35" s="76"/>
-      <c r="S35" s="77"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="75"/>
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+      <c r="I35" s="75"/>
+      <c r="J35" s="75"/>
+      <c r="K35" s="76"/>
+      <c r="M35" s="74"/>
+      <c r="N35" s="75"/>
+      <c r="O35" s="75"/>
+      <c r="P35" s="75"/>
+      <c r="Q35" s="75"/>
+      <c r="R35" s="75"/>
+      <c r="S35" s="76"/>
     </row>
     <row r="36" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E36" s="75"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="76"/>
-      <c r="K36" s="77"/>
-      <c r="M36" s="75"/>
-      <c r="N36" s="76"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="76"/>
-      <c r="Q36" s="76"/>
-      <c r="R36" s="76"/>
-      <c r="S36" s="77"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="75"/>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+      <c r="I36" s="75"/>
+      <c r="J36" s="75"/>
+      <c r="K36" s="76"/>
+      <c r="M36" s="74"/>
+      <c r="N36" s="75"/>
+      <c r="O36" s="75"/>
+      <c r="P36" s="75"/>
+      <c r="Q36" s="75"/>
+      <c r="R36" s="75"/>
+      <c r="S36" s="76"/>
     </row>
     <row r="37" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E37" s="75"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="76"/>
-      <c r="K37" s="77"/>
-      <c r="M37" s="75"/>
-      <c r="N37" s="76"/>
-      <c r="O37" s="76"/>
-      <c r="P37" s="76"/>
-      <c r="Q37" s="76"/>
-      <c r="R37" s="76"/>
-      <c r="S37" s="77"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="76"/>
+      <c r="M37" s="74"/>
+      <c r="N37" s="75"/>
+      <c r="O37" s="75"/>
+      <c r="P37" s="75"/>
+      <c r="Q37" s="75"/>
+      <c r="R37" s="75"/>
+      <c r="S37" s="76"/>
     </row>
     <row r="38" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E38" s="75"/>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="76"/>
-      <c r="K38" s="77"/>
-      <c r="M38" s="75"/>
-      <c r="N38" s="76"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="76"/>
-      <c r="Q38" s="76"/>
-      <c r="R38" s="76"/>
-      <c r="S38" s="77"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="75"/>
+      <c r="G38" s="75"/>
+      <c r="H38" s="75"/>
+      <c r="I38" s="75"/>
+      <c r="J38" s="75"/>
+      <c r="K38" s="76"/>
+      <c r="M38" s="74"/>
+      <c r="N38" s="75"/>
+      <c r="O38" s="75"/>
+      <c r="P38" s="75"/>
+      <c r="Q38" s="75"/>
+      <c r="R38" s="75"/>
+      <c r="S38" s="76"/>
     </row>
     <row r="39" spans="5:19" x14ac:dyDescent="0.25">
-      <c r="E39" s="75"/>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
-      <c r="I39" s="76"/>
-      <c r="J39" s="76"/>
-      <c r="K39" s="77"/>
-      <c r="M39" s="75"/>
-      <c r="N39" s="76"/>
-      <c r="O39" s="76"/>
-      <c r="P39" s="76"/>
-      <c r="Q39" s="76"/>
-      <c r="R39" s="76"/>
-      <c r="S39" s="77"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="75"/>
+      <c r="G39" s="75"/>
+      <c r="H39" s="75"/>
+      <c r="I39" s="75"/>
+      <c r="J39" s="75"/>
+      <c r="K39" s="76"/>
+      <c r="M39" s="74"/>
+      <c r="N39" s="75"/>
+      <c r="O39" s="75"/>
+      <c r="P39" s="75"/>
+      <c r="Q39" s="75"/>
+      <c r="R39" s="75"/>
+      <c r="S39" s="76"/>
     </row>
     <row r="40" spans="5:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E40" s="78"/>
-      <c r="F40" s="79"/>
-      <c r="G40" s="79"/>
-      <c r="H40" s="79"/>
-      <c r="I40" s="79"/>
-      <c r="J40" s="79"/>
-      <c r="K40" s="80"/>
-      <c r="M40" s="78"/>
-      <c r="N40" s="79"/>
-      <c r="O40" s="79"/>
-      <c r="P40" s="79"/>
-      <c r="Q40" s="79"/>
-      <c r="R40" s="79"/>
-      <c r="S40" s="80"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
+      <c r="J40" s="78"/>
+      <c r="K40" s="79"/>
+      <c r="M40" s="77"/>
+      <c r="N40" s="78"/>
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="78"/>
+      <c r="R40" s="78"/>
+      <c r="S40" s="79"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="cdv/AvFh6srGwbB7utym/s5Rto4SgYVsrqY0f4ta+9TA3R9+USfKRAEajm2Nsa5BKLVlVu6MEYwkKIOOzax3VA==" saltValue="19VEwvYrnvwxOou5gDKwaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="14">
-    <mergeCell ref="F8:K8"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:I4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="F7:K7"/>
     <mergeCell ref="M29:S40"/>
     <mergeCell ref="B30:C32"/>
     <mergeCell ref="F9:K9"/>
@@ -4148,6 +4303,12 @@
     <mergeCell ref="B13:C14"/>
     <mergeCell ref="B25:C28"/>
     <mergeCell ref="E29:K40"/>
+    <mergeCell ref="F8:K8"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:I4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="F7:K7"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1" display="Video" xr:uid="{299DFAA1-25BE-465C-8E9D-C2A88F14D04A}"/>
@@ -4158,7 +4319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9584C558-284C-4C93-9D27-3C3A07464280}">
   <dimension ref="B2:S22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4172,34 +4333,34 @@
     <row r="2" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="64" t="s">
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="63" t="s">
         <v>42</v>
       </c>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="65"/>
-      <c r="M4" s="81" t="s">
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="64"/>
+      <c r="M4" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="82"/>
+      <c r="N4" s="81"/>
     </row>
     <row r="5" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="66"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="68"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="67"/>
       <c r="M5" s="3" t="s">
         <v>9</v>
       </c>
@@ -4208,15 +4369,15 @@
       </c>
     </row>
     <row r="6" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="66"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="70"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="71"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="70"/>
       <c r="M6" s="5" t="s">
         <v>11</v>
       </c>
@@ -4225,20 +4386,20 @@
       </c>
     </row>
     <row r="7" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="69"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="47">
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="46">
         <f>Soln!C23</f>
         <v>0</v>
       </c>
-      <c r="G7" s="111" t="s">
+      <c r="G7" s="119" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="113"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
       <c r="M7" s="7" t="s">
         <v>13</v>
       </c>
@@ -4247,17 +4408,17 @@
       </c>
     </row>
     <row r="8" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="117" t="s">
+      <c r="B8" s="109" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="111"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="51"/>
       <c r="M8" s="8" t="s">
         <v>15</v>
       </c>
@@ -4266,20 +4427,20 @@
       </c>
     </row>
     <row r="9" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="120"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="129"/>
-      <c r="F9" s="46">
+      <c r="B9" s="112"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="45">
         <f>1.5*F7</f>
         <v>0</v>
       </c>
-      <c r="G9" s="111" t="s">
+      <c r="G9" s="119" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="113"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="121"/>
       <c r="M9" s="9" t="s">
         <v>17</v>
       </c>
@@ -4288,244 +4449,243 @@
       </c>
     </row>
     <row r="10" spans="2:19" ht="20.100000000000001" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="123"/>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="53"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="116"/>
+      <c r="D10" s="116"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="51"/>
     </row>
     <row r="11" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="117" t="s">
+      <c r="B11" s="109" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="53"/>
+      <c r="C11" s="110"/>
+      <c r="D11" s="110"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="51"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
-      <c r="M11" s="107" t="s">
+      <c r="M11" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="108"/>
-      <c r="O11" s="108"/>
-      <c r="P11" s="108"/>
-      <c r="Q11" s="108"/>
-      <c r="R11" s="108"/>
-      <c r="S11" s="109"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="107"/>
+      <c r="P11" s="107"/>
+      <c r="Q11" s="107"/>
+      <c r="R11" s="107"/>
+      <c r="S11" s="108"/>
     </row>
     <row r="12" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="120"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="129"/>
-      <c r="F12" s="48" t="e">
+      <c r="B12" s="112"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="47" t="e">
         <f>F7/F9</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G12" s="126" t="s">
+      <c r="G12" s="122" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="127"/>
-      <c r="I12" s="127"/>
-      <c r="J12" s="128"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="124"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
-      <c r="M12" s="32">
+      <c r="M12" s="31">
         <v>15</v>
       </c>
-      <c r="N12" s="86" t="s">
+      <c r="N12" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="O12" s="87"/>
-      <c r="P12" s="87"/>
-      <c r="Q12" s="87"/>
-      <c r="R12" s="87"/>
-      <c r="S12" s="88"/>
+      <c r="O12" s="86"/>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="86"/>
+      <c r="R12" s="86"/>
+      <c r="S12" s="87"/>
     </row>
     <row r="13" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="123"/>
-      <c r="C13" s="124"/>
-      <c r="D13" s="124"/>
-      <c r="E13" s="125"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="53"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="49"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="51"/>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
-      <c r="M13" s="29">
+      <c r="M13" s="28">
         <v>15</v>
       </c>
-      <c r="N13" s="89" t="s">
+      <c r="N13" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="91"/>
+      <c r="O13" s="89"/>
+      <c r="P13" s="89"/>
+      <c r="Q13" s="89"/>
+      <c r="R13" s="89"/>
+      <c r="S13" s="90"/>
     </row>
     <row r="14" spans="2:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="53"/>
-      <c r="M14" s="30">
+      <c r="C14" s="110"/>
+      <c r="D14" s="110"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="51"/>
+      <c r="M14" s="29">
         <v>16</v>
       </c>
-      <c r="N14" s="86" t="s">
+      <c r="N14" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="O14" s="87"/>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="88"/>
+      <c r="O14" s="86"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="86"/>
+      <c r="R14" s="86"/>
+      <c r="S14" s="87"/>
     </row>
     <row r="15" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="120"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="129"/>
-      <c r="F15" s="46">
+      <c r="B15" s="112"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="45">
         <f>F9*(1+10%)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="111" t="s">
+      <c r="G15" s="119" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="112"/>
-      <c r="I15" s="112"/>
-      <c r="J15" s="113"/>
-      <c r="M15" s="31">
+      <c r="H15" s="120"/>
+      <c r="I15" s="120"/>
+      <c r="J15" s="121"/>
+      <c r="M15" s="30">
         <v>16</v>
       </c>
-      <c r="N15" s="98" t="s">
+      <c r="N15" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="O15" s="99"/>
-      <c r="P15" s="99"/>
-      <c r="Q15" s="99"/>
-      <c r="R15" s="99"/>
-      <c r="S15" s="100"/>
+      <c r="O15" s="98"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="98"/>
+      <c r="R15" s="98"/>
+      <c r="S15" s="99"/>
     </row>
     <row r="16" spans="2:19" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="123"/>
-      <c r="C16" s="124"/>
-      <c r="D16" s="124"/>
-      <c r="E16" s="125"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="53"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="51"/>
     </row>
     <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="117" t="s">
+      <c r="B17" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="118"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="53"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="110"/>
+      <c r="E17" s="111"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="51"/>
     </row>
     <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="120"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="129"/>
-      <c r="F18" s="46" t="e">
+      <c r="B18" s="112"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="45" t="e">
         <f>F12*F15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G18" s="111" t="s">
+      <c r="G18" s="119" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="112"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="113"/>
+      <c r="H18" s="120"/>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
     </row>
     <row r="19" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="123"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="124"/>
-      <c r="E19" s="125"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="53"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="51"/>
     </row>
     <row r="20" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="117" t="s">
+      <c r="B20" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="53"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="51"/>
     </row>
     <row r="21" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="120"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="121"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="45" t="e">
+      <c r="B21" s="112"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="44" t="e">
         <f>F18/F7-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G21" s="111" t="s">
+      <c r="G21" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="H21" s="112"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="113"/>
+      <c r="H21" s="120"/>
+      <c r="I21" s="120"/>
+      <c r="J21" s="121"/>
     </row>
     <row r="22" spans="2:10" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="123"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="124"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="44"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="53"/>
+      <c r="I22" s="53"/>
+      <c r="J22" s="43"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="tmZVzQuchFx4+hmWgpIJ/Xs+dtJHoEIpggrKQwV2riBVXZncjb+E//66rxwrmYGvYjZ14gUZB8TBJFFIqvUKmQ==" saltValue="gVCYbawCFDlVV36UwKuBGA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="19">
-    <mergeCell ref="B4:E7"/>
-    <mergeCell ref="F4:J6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="B8:E10"/>
-    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B17:E19"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="B20:E22"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="B11:E13"/>
     <mergeCell ref="M11:S11"/>
     <mergeCell ref="G12:J12"/>
     <mergeCell ref="N12:S12"/>
@@ -4534,18 +4694,19 @@
     <mergeCell ref="N14:S14"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="N15:S15"/>
-    <mergeCell ref="B17:E19"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="B20:E22"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="B11:E13"/>
+    <mergeCell ref="B4:E7"/>
+    <mergeCell ref="F4:J6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="B8:E10"/>
+    <mergeCell ref="G9:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4195EBF3-0FAD-4706-960B-09E10EE200F7}">
   <dimension ref="B2:N18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4567,93 +4728,93 @@
         <v>41</v>
       </c>
       <c r="H3" s="130"/>
-      <c r="J3" s="83" t="s">
+      <c r="J3" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="K3" s="64"/>
-      <c r="L3" s="64"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="65"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="64"/>
     </row>
     <row r="4" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="121"/>
-      <c r="J4" s="66"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="68"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="66"/>
+      <c r="L4" s="66"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="67"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="113"/>
+      <c r="E5" s="113"/>
       <c r="F5" s="12"/>
       <c r="G5" s="130" t="s">
         <v>44</v>
       </c>
       <c r="H5" s="130"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="68"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="113"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="113"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="67"/>
     </row>
     <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="121"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="71"/>
+      <c r="C7" s="113"/>
+      <c r="D7" s="113"/>
+      <c r="E7" s="113"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="70"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="121"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
       <c r="F8" s="12"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="121"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="121"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="113"/>
+      <c r="D9" s="113"/>
+      <c r="E9" s="113"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="121" t="s">
+      <c r="B10" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
+      <c r="C10" s="113"/>
+      <c r="D10" s="113"/>
+      <c r="E10" s="113"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="121"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="121"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113"/>
       <c r="F11" s="12"/>
       <c r="G11" s="130" t="s">
         <v>47</v>
@@ -4665,32 +4826,32 @@
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="121"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="121"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="121"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="121"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="121"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
       <c r="F14" s="12"/>
       <c r="G14" s="130" t="s">
         <v>49</v>
@@ -4698,24 +4859,24 @@
       <c r="H14" s="130"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="121"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
     </row>
     <row r="16" spans="2:14" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="121" t="s">
+      <c r="B16" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="121"/>
-      <c r="D16" s="121"/>
-      <c r="E16" s="121"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="113"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="113"/>
       <c r="F17" s="12"/>
       <c r="G17" s="130" t="s">
         <v>51</v>
@@ -4724,10 +4885,10 @@
       <c r="I17" s="130"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="121"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="121"/>
-      <c r="E18" s="121"/>
+      <c r="B18" s="113"/>
+      <c r="C18" s="113"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4748,7 +4909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5EB4D9-71EF-4324-90BE-671090B5BF3E}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4819,25 +4980,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -5054,25 +5196,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9BBA8FE-E6DA-4827-85B8-6FA8D6DB8DFA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{619E3EE9-834C-43AE-8A34-8B87F1488608}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1549A78A-B0D3-45CB-AB15-676AD9DAC4AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5089,4 +5232,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{619E3EE9-834C-43AE-8A34-8B87F1488608}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9BBA8FE-E6DA-4827-85B8-6FA8D6DB8DFA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>